--- a/academias/Programación - Estadisticos 20211.xlsx
+++ b/academias/Programación - Estadisticos 20211.xlsx
@@ -498,25 +498,25 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>80.95</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>19.05</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>19.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -533,25 +533,25 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>73.68000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="H3">
-        <v>26.32</v>
+        <v>13.16</v>
       </c>
       <c r="I3">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>26.32</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -568,25 +568,25 @@
         <v>25</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="H4">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I4">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="J4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -603,25 +603,25 @@
         <v>26</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>65.38</v>
+        <v>92.31</v>
       </c>
       <c r="H5">
-        <v>34.62</v>
+        <v>7.69</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>34.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -638,25 +638,25 @@
         <v>25</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I6">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -673,25 +673,25 @@
         <v>26</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>80.77</v>
+        <v>84.62</v>
       </c>
       <c r="H7">
-        <v>19.23</v>
+        <v>15.38</v>
       </c>
       <c r="I7">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>19.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -708,25 +708,25 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>80.95</v>
+        <v>90.48</v>
       </c>
       <c r="H8">
-        <v>19.05</v>
+        <v>9.52</v>
       </c>
       <c r="I8">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>19.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -743,25 +743,25 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>65.79000000000001</v>
+        <v>81.58</v>
       </c>
       <c r="H9">
-        <v>34.21</v>
+        <v>18.42</v>
       </c>
       <c r="I9">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J9">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>34.21</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -827,22 +827,25 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>8.6</v>
       </c>
       <c r="J2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -859,22 +862,25 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>86.84</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>13.16</v>
+      </c>
+      <c r="I3">
+        <v>8.5</v>
       </c>
       <c r="J3">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>100</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -891,22 +897,25 @@
         <v>25</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>32</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -923,22 +932,25 @@
         <v>26</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>11.54</v>
+      </c>
+      <c r="I5">
+        <v>8.5</v>
       </c>
       <c r="J5">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -955,22 +967,25 @@
         <v>25</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I6">
+        <v>7.7</v>
       </c>
       <c r="J6">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -987,22 +1002,25 @@
         <v>26</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>84.62</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>15.38</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1019,22 +1037,25 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>90.48</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>9.52</v>
+      </c>
+      <c r="I8">
+        <v>7.8</v>
       </c>
       <c r="J8">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1051,22 +1072,25 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>81.58</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>18.42</v>
+      </c>
+      <c r="I9">
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>18.42</v>
       </c>
     </row>
   </sheetData>
@@ -1132,25 +1156,25 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>80.95</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>19.05</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>8.6</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>19.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1167,25 +1191,25 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>73.68000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="H3">
-        <v>26.32</v>
+        <v>13.16</v>
       </c>
       <c r="I3">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>26.32</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1202,25 +1226,25 @@
         <v>25</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="H4">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I4">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1237,25 +1261,25 @@
         <v>26</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>65.38</v>
+        <v>92.31</v>
       </c>
       <c r="H5">
-        <v>34.62</v>
+        <v>7.69</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>34.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1272,25 +1296,25 @@
         <v>25</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1307,25 +1331,25 @@
         <v>26</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>80.77</v>
+        <v>84.62</v>
       </c>
       <c r="H7">
-        <v>19.23</v>
+        <v>15.38</v>
       </c>
       <c r="I7">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>19.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1342,25 +1366,25 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>80.95</v>
+        <v>90.48</v>
       </c>
       <c r="H8">
-        <v>19.05</v>
+        <v>9.52</v>
       </c>
       <c r="I8">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>19.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1377,25 +1401,25 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>65.79000000000001</v>
+        <v>81.58</v>
       </c>
       <c r="H9">
-        <v>34.21</v>
+        <v>18.42</v>
       </c>
       <c r="I9">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J9">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>34.21</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Programación - Estadisticos 20211.xlsx
+++ b/academias/Programación - Estadisticos 20211.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
     <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="3er Parcial" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -91,6 +91,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -143,8 +147,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -445,42 +451,45 @@
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -503,19 +512,19 @@
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>100</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
         <v>8.4</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -538,19 +547,19 @@
       <c r="F3">
         <v>5</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>86.84</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>13.16</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J3">
         <v>5</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>13.16</v>
       </c>
     </row>
@@ -573,19 +582,19 @@
       <c r="F4">
         <v>7</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>72</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>28</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>7.1</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -608,19 +617,19 @@
       <c r="F5">
         <v>2</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>92.31</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>7.69</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>6.7</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -643,19 +652,19 @@
       <c r="F6">
         <v>3</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>88</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>12</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>6.5</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -678,19 +687,19 @@
       <c r="F7">
         <v>4</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>84.62</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>15.38</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>6.3</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -713,19 +722,19 @@
       <c r="F8">
         <v>2</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>90.48</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>9.52</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>8</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -748,19 +757,19 @@
       <c r="F9">
         <v>7</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>81.58</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>18.42</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>7.8</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -774,42 +783,45 @@
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -832,19 +844,19 @@
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>100</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
         <v>8.6</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -867,19 +879,19 @@
       <c r="F3">
         <v>5</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>86.84</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>13.16</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>8.5</v>
       </c>
       <c r="J3">
         <v>5</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>13.16</v>
       </c>
     </row>
@@ -902,19 +914,19 @@
       <c r="F4">
         <v>8</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>68</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>32</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>8</v>
       </c>
       <c r="J4">
         <v>8</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>32</v>
       </c>
     </row>
@@ -937,19 +949,19 @@
       <c r="F5">
         <v>3</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>88.45999999999999</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>11.54</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>8.5</v>
       </c>
       <c r="J5">
         <v>3</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>11.54</v>
       </c>
     </row>
@@ -972,19 +984,19 @@
       <c r="F6">
         <v>5</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>80</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>20</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>7.7</v>
       </c>
       <c r="J6">
         <v>5</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>20</v>
       </c>
     </row>
@@ -1007,19 +1019,19 @@
       <c r="F7">
         <v>4</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>84.62</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>15.38</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>7</v>
       </c>
       <c r="J7">
         <v>2</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>7.69</v>
       </c>
     </row>
@@ -1042,19 +1054,19 @@
       <c r="F8">
         <v>2</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>90.48</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>9.52</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>7.8</v>
       </c>
       <c r="J8">
         <v>2</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>9.52</v>
       </c>
     </row>
@@ -1077,19 +1089,19 @@
       <c r="F9">
         <v>7</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>81.58</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>18.42</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J9">
         <v>7</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>18.42</v>
       </c>
     </row>
@@ -1103,42 +1115,45 @@
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1161,19 +1176,19 @@
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>100</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
         <v>8.6</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1196,19 +1211,19 @@
       <c r="F3">
         <v>5</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>86.84</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>13.16</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J3">
         <v>5</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>13.16</v>
       </c>
     </row>
@@ -1231,19 +1246,19 @@
       <c r="F4">
         <v>7</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>72</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>28</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>7.3</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1266,19 +1281,19 @@
       <c r="F5">
         <v>2</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>92.31</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>7.69</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>7.5</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1301,19 +1316,19 @@
       <c r="F6">
         <v>3</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>88</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>12</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>7</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1336,19 +1351,19 @@
       <c r="F7">
         <v>4</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>84.62</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>15.38</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>6.7</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1371,19 +1386,19 @@
       <c r="F8">
         <v>2</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>90.48</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>9.52</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>8</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1406,19 +1421,19 @@
       <c r="F9">
         <v>7</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>81.58</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>18.42</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>7.8</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Programación - Estadisticos 20211.xlsx
+++ b/academias/Programación - Estadisticos 20211.xlsx
@@ -92,7 +92,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">

--- a/academias/Programación - Estadisticos 20211.xlsx
+++ b/academias/Programación - Estadisticos 20211.xlsx
@@ -542,25 +542,25 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>86.84</v>
+        <v>89.47</v>
       </c>
       <c r="H3" s="1">
-        <v>13.16</v>
+        <v>10.53</v>
       </c>
       <c r="I3" s="2">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>13.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -874,25 +874,25 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>86.84</v>
+        <v>89.47</v>
       </c>
       <c r="H3" s="1">
-        <v>13.16</v>
+        <v>10.53</v>
       </c>
       <c r="I3" s="2">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>13.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -909,25 +909,25 @@
         <v>25</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H4" s="1">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I4" s="2">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -944,25 +944,25 @@
         <v>26</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>88.45999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="H5" s="1">
-        <v>11.54</v>
+        <v>7.69</v>
       </c>
       <c r="I5" s="2">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>11.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -979,25 +979,25 @@
         <v>25</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H6" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I6" s="2">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1026,13 +1026,13 @@
         <v>15.38</v>
       </c>
       <c r="I7" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>7.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1049,25 +1049,25 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>90.48</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>9.52</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
         <v>7.8</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>9.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1084,25 +1084,25 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>81.58</v>
+        <v>89.47</v>
       </c>
       <c r="H9" s="1">
-        <v>18.42</v>
+        <v>10.53</v>
       </c>
       <c r="I9" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J9">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>18.42</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1183,7 +1183,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1206,25 +1206,25 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>86.84</v>
+        <v>89.47</v>
       </c>
       <c r="H3" s="1">
-        <v>13.16</v>
+        <v>10.53</v>
       </c>
       <c r="I3" s="2">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>13.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1253,7 +1253,7 @@
         <v>28</v>
       </c>
       <c r="I4" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1276,19 +1276,19 @@
         <v>26</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>92.31</v>
+        <v>84.62</v>
       </c>
       <c r="H5" s="1">
-        <v>7.69</v>
+        <v>15.38</v>
       </c>
       <c r="I5" s="2">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1311,16 +1311,16 @@
         <v>25</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="H6" s="1">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I6" s="2">
         <v>7</v>
@@ -1358,7 +1358,7 @@
         <v>15.38</v>
       </c>
       <c r="I7" s="2">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1381,19 +1381,19 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>90.48</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>9.52</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1416,16 +1416,16 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>81.58</v>
+        <v>89.47</v>
       </c>
       <c r="H9" s="1">
-        <v>18.42</v>
+        <v>10.53</v>
       </c>
       <c r="I9" s="2">
         <v>7.8</v>
